--- a/naver-place-crawler/results_nail/춘천_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/춘천_네일샵.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2241</v>
+        <v>2257</v>
       </c>
       <c r="Q2" t="n">
         <v>42</v>
       </c>
       <c r="R2" t="n">
-        <v>2283</v>
+        <v>2299</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="Q3" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="R3" t="n">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>춘천댁네일</t>
+          <t>네일구름 후평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>shj1342@naver.com</t>
+          <t>jinkyeong97@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1334-8446</t>
+          <t>0507-1412-1769</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 중앙로67번길 18 2층 1204호 춘천댁네일</t>
+          <t>강원 춘천시 성심로 17 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chchdnail_yul</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -798,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcf0ry</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,17 +809,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1717</v>
+        <v>402</v>
       </c>
       <c r="Q4" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1787</v>
+        <v>407</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1718046085</t>
+          <t>2086216127</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1718046085</t>
+          <t>https://m.place.naver.com/place/2086216127</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -854,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아빈느네일</t>
+          <t>뮤네일 춘천명동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kiyeon515@naver.com</t>
+          <t>fine5173@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1495-1901</t>
+          <t>0507-1351-7532</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 방송길 77 모다아울렛 2층 2253호</t>
+          <t>강원 춘천시 중앙로67번길 18 4동 1층 4110호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbxawExb</t>
+          <t>https://www.instagram.com/_luv_mu?igsh=a3h4eXBnOTBjbGxr&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -896,13 +892,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w8x2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="Q5" t="n">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>426</v>
+        <v>302</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>31229640</t>
+          <t>1156492391</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229640</t>
+          <t>https://m.place.naver.com/place/1156492391</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -948,34 +948,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뮤네일 춘천명동점</t>
+          <t>아빈느네일</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fine5173@naver.com</t>
+          <t>kiyeon515@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1351-7532</t>
+          <t>0507-1495-1901</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 중앙로67번길 18 4동 1층 4110호</t>
+          <t>강원 춘천시 방송길 77 모다아울렛 2층 2253호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_luv_mu?igsh=a3h4eXBnOTBjbGxr&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xbxawExb</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -990,17 +990,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5w8x2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>173</v>
       </c>
       <c r="R6" t="n">
-        <v>297</v>
+        <v>437</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1020,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1156492391</t>
+          <t>31229640</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156492391</t>
+          <t>https://m.place.naver.com/place/31229640</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1047,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kkoung1001@naver.com</t>
+          <t>bongbong323@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1103,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1128,7 +1124,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1201,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q8" t="n">
         <v>39</v>
       </c>
       <c r="R8" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1226,7 +1222,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1238,34 +1234,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공감네일</t>
+          <t>엘네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>finger1229@naver.com</t>
+          <t>dalmee0224@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1307-2741</t>
+          <t>0507-1488-1590</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>강원 춘천시 안마산로 116 102호</t>
+          <t>강원 춘천시 안마산로 110 하윤빌딩 5층 엘네일</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/finger1229</t>
+          <t>http://pf.kakao.com/_NlVXK</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1275,18 +1271,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vkiq</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>182</v>
+        <v>289</v>
       </c>
       <c r="Q9" t="n">
-        <v>65</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1332500407</t>
+          <t>1180347602</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332500407</t>
+          <t>https://m.place.naver.com/place/1180347602</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R10" t="n">
-        <v>508</v>
+        <v>530</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q11" t="n">
         <v>220</v>
       </c>
       <c r="R11" t="n">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/춘천_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/춘천_네일샵.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="37" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2257</v>
+        <v>2262</v>
       </c>
       <c r="Q2" t="n">
         <v>42</v>
       </c>
       <c r="R2" t="n">
-        <v>2299</v>
+        <v>2304</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -658,24 +658,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>더 빛나는 네일</t>
+          <t>네일구름 후평점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>wseok0131@naver.com</t>
+          <t>jinkyeong97@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1431-4277</t>
+          <t>0507-1412-1769</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 춘천시 벌말길 53 1층 102호</t>
+          <t>강원 춘천시 성심로 17 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5um7s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>208</v>
+        <v>416</v>
       </c>
       <c r="Q3" t="n">
-        <v>296</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>504</v>
+        <v>421</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1737683039</t>
+          <t>2086216127</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737683039</t>
+          <t>https://m.place.naver.com/place/2086216127</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -756,24 +752,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일구름 후평점</t>
+          <t>더 빛나는 네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jinkyeong97@naver.com</t>
+          <t>wseok0131@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1412-1769</t>
+          <t>0507-1431-4277</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 성심로 17 1층</t>
+          <t>강원 춘천시 벌말길 53 1층 102호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +794,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5um7s</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>402</v>
+        <v>209</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>296</v>
       </c>
       <c r="R4" t="n">
-        <v>407</v>
+        <v>505</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2086216127</t>
+          <t>1737683039</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086216127</t>
+          <t>https://m.place.naver.com/place/1737683039</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -850,34 +850,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>뮤네일 춘천명동점</t>
+          <t>투리뷰티 춘천점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fine5173@naver.com</t>
+          <t>twolee_cc@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1351-7532</t>
+          <t>0507-1444-2733</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>강원 춘천시 중앙로67번길 18 4동 1층 4110호</t>
+          <t>강원 춘천시 시청길10번길 6 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_luv_mu?igsh=a3h4eXBnOTBjbGxr&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_VWxacxj/chat</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w8x2</t>
+          <t>https://talk.naver.com/ct/w41gqt</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -911,14 +911,14 @@
         </is>
       </c>
       <c r="P5" t="n">
+        <v>252</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>39</v>
+      </c>
+      <c r="R5" t="n">
         <v>291</v>
       </c>
-      <c r="Q5" t="n">
-        <v>11</v>
-      </c>
-      <c r="R5" t="n">
-        <v>302</v>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>X</t>
@@ -926,17 +926,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1156492391</t>
+          <t>1013387727</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156492391</t>
+          <t>https://m.place.naver.com/place/1013387727</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -948,34 +948,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>아빈느네일</t>
+          <t>뮤네일 춘천명동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kiyeon515@naver.com</t>
+          <t>fine5173@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1495-1901</t>
+          <t>0507-1351-7532</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 방송길 77 모다아울렛 2층 2253호</t>
+          <t>강원 춘천시 중앙로67번길 18 4동 1층 4110호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbxawExb</t>
+          <t>https://www.instagram.com/_luv_mu?igsh=a3h4eXBnOTBjbGxr&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -990,13 +990,17 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w8x2</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1005,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="Q6" t="n">
-        <v>173</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>437</v>
+        <v>303</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1020,17 +1024,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>31229640</t>
+          <t>1156492391</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31229640</t>
+          <t>https://m.place.naver.com/place/1156492391</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1099,13 +1103,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q7" t="n">
         <v>100</v>
       </c>
       <c r="R7" t="n">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1124,7 +1128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,34 +1140,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>투리뷰티 춘천점</t>
+          <t>프린세스 네일</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>twolee_cc@naver.com</t>
+          <t>csy1004did@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1444-2733</t>
+          <t>0507-1367-4222</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>강원 춘천시 시청길10번길 6 2층</t>
+          <t>강원 춘천시 중앙로67번길 18 브라운가 6동 6109호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_VWxacxj/chat</t>
+          <t>https://www.instagram.com/_princess_c.c</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1178,14 +1182,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w41gqt</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>O</t>
@@ -1197,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="Q8" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="R8" t="n">
-        <v>291</v>
+        <v>383</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,17 +1212,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1013387727</t>
+          <t>1212227767</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1013387727</t>
+          <t>https://m.place.naver.com/place/1212227767</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q9" t="n">
         <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1332,29 +1332,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>언네일 춘천퇴계점</t>
+          <t>레푸스 춘천석사점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mryiew@naver.com</t>
+          <t>lightrose77@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1471-0319</t>
+          <t>0507-1429-9952</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>강원 춘천시 퇴계로 129 1층 언네일</t>
+          <t>강원 춘천시 후석로 16 서진빌딩 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xbAxaUs</t>
+          <t>http://pf.kakao.com/_xdtxdvxb</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgzgen7</t>
+          <t>https://talk.naver.com/ct/w40m38</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1393,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>520</v>
+        <v>400</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="R10" t="n">
-        <v>530</v>
+        <v>620</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1750956436</t>
+          <t>1258918439</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1750956436</t>
+          <t>https://m.place.naver.com/place/1258918439</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1430,34 +1430,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레푸스 춘천석사점</t>
+          <t>네일포그</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lightrose77@naver.com</t>
+          <t>bambi_showpu@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1429-9952</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원 춘천시 후석로 16 서진빌딩 2층</t>
+          <t>강원 춘천시 서부대성로 165 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xdtxdvxb</t>
+          <t>https://www.instagram.com/nailfog?igsh=MTh1MmU2dDN3amxx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1472,17 +1468,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40m38</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1491,13 +1483,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>400</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>620</v>
+        <v>11</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,17 +1498,303 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1258918439</t>
+          <t>2044306446</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258918439</t>
+          <t>https://m.place.naver.com/place/2044306446</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>네일엔딩</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hayul_hana@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1310-7557</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>강원 춘천시 춘천로138번길 16 상가동 1층 105호 네일엔딩</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm3nqr9</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>21</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2015880167</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2015880167</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>무드스튜디오 네일</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>soyeon1341@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1330-7897</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>강원 춘천시 방송길 77 2256호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/moodstudio_nail</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wluclty</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2084939235</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084939235</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>네일을이루다</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>together70jhm@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>강원 춘천시 효명길 27-1 상가동 1층 1호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/2ruda_nail?igsh=OHNoc2VtbmhhZWRy</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2066945171</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2066945171</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/춘천_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/춘천_네일샵.xlsx
@@ -564,29 +564,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>네일구름 춘천온의점</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>fine5173@naver.com</t>
-        </is>
-      </c>
+          <t>더 빛나는 네일</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1484-0062</t>
+          <t>0507-1431-4277</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>강원 춘천시 방송길 77 모다아울렛 1층 1240호 네일,구름</t>
+          <t>강원 춘천시 벌말길 53 1층 102호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_gureum</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +592,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +602,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5um7s</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2262</v>
+        <v>209</v>
       </c>
       <c r="Q2" t="n">
-        <v>42</v>
+        <v>296</v>
       </c>
       <c r="R2" t="n">
-        <v>2304</v>
+        <v>505</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1814262310</t>
+          <t>1737683039</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814262310</t>
+          <t>https://m.place.naver.com/place/1737683039</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>네일구름 후평점</t>
+          <t>네일구름 춘천온의점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jinkyeong97@naver.com</t>
+          <t>fine5173@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1412-1769</t>
+          <t>0507-1484-0062</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>강원 춘천시 성심로 17 1층</t>
+          <t>강원 춘천시 방송길 77 모다아울렛 1층 1240호 네일,구름</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://instagram.com/nail_gureum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>416</v>
+        <v>2262</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="R3" t="n">
-        <v>421</v>
+        <v>2304</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2086216127</t>
+          <t>1814262310</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086216127</t>
+          <t>https://m.place.naver.com/place/1814262310</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -752,24 +752,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더 빛나는 네일</t>
+          <t>네일구름 후평점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>wseok0131@naver.com</t>
+          <t>jinkyeong97@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1431-4277</t>
+          <t>0507-1412-1769</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>강원 춘천시 벌말길 53 1층 102호</t>
+          <t>강원 춘천시 성심로 17 1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5um7s</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>209</v>
+        <v>416</v>
       </c>
       <c r="Q4" t="n">
-        <v>296</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>505</v>
+        <v>421</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1737683039</t>
+          <t>2086216127</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1737683039</t>
+          <t>https://m.place.naver.com/place/2086216127</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -948,34 +944,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뮤네일 춘천명동점</t>
+          <t>언네일 춘천퇴계점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fine5173@naver.com</t>
+          <t>mryiew@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1351-7532</t>
+          <t>0507-1471-0319</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>강원 춘천시 중앙로67번길 18 4동 1층 4110호</t>
+          <t>강원 춘천시 퇴계로 129 1층 언네일</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_luv_mu?igsh=a3h4eXBnOTBjbGxr&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_xbAxaUs</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,12 +991,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w8x2</t>
+          <t>https://talk.naver.com/ct/wgzgen7</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1009,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>292</v>
+        <v>522</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R6" t="n">
-        <v>303</v>
+        <v>532</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,12 +1020,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1156492391</t>
+          <t>1750956436</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156492391</t>
+          <t>https://m.place.naver.com/place/1750956436</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1197,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q8" t="n">
         <v>125</v>
       </c>
       <c r="R8" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1237,11 +1233,7 @@
           <t>엘네일</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dalmee0224@naver.com</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
@@ -1430,25 +1422,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일포그</t>
+          <t>네일엔딩</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bambi_showpu@naver.com</t>
+          <t>hayul_hana@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1310-7557</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>강원 춘천시 서부대성로 165 1층</t>
+          <t>강원 춘천시 춘천로138번길 16 상가동 1층 105호 네일엔딩</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailfog?igsh=MTh1MmU2dDN3amxx&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1458,7 +1454,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1468,10 +1464,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wm3nqr9</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2044306446</t>
+          <t>2015880167</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2044306446</t>
+          <t>https://m.place.naver.com/place/2015880167</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1520,29 +1520,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>네일엔딩</t>
+          <t>네일포그</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hayul_hana@naver.com</t>
+          <t>bambi_showpu@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1310-7557</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>강원 춘천시 춘천로138번길 16 상가동 1층 105호 네일엔딩</t>
+          <t>강원 춘천시 서부대성로 165 1층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailfog?igsh=MTh1MmU2dDN3amxx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1552,7 +1548,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1562,14 +1558,10 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wm3nqr9</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1577,17 +1569,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1596,12 +1588,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2015880167</t>
+          <t>2044306446</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015880167</t>
+          <t>https://m.place.naver.com/place/2044306446</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1621,11 +1613,7 @@
           <t>무드스튜디오 네일</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>soyeon1341@naver.com</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
